--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261013.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261013.xlsx
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>7,137,000</t>
+          <t>585,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>585,000</t>
+          <t>7,137,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>4,884,400</t>
+          <t>42,300,500</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>42,300,500</t>
+          <t>4,884,400</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>17,681,000</t>
+          <t>50,331,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>50,331,000</t>
+          <t>17,681,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
